--- a/AAII_Financials/Yearly/RITM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RITM_YR_FIN.xlsx
@@ -937,7 +937,7 @@
         <v>13900</v>
       </c>
       <c r="E14" s="3">
-        <v>-9600</v>
+        <v>-27400</v>
       </c>
       <c r="F14" s="3">
         <v>32900</v>
@@ -1029,7 +1029,7 @@
         <v>2960200</v>
       </c>
       <c r="E17" s="3">
-        <v>2511100</v>
+        <v>2528900</v>
       </c>
       <c r="F17" s="3">
         <v>1585800</v>
@@ -1068,7 +1068,7 @@
         <v>820300</v>
       </c>
       <c r="E18" s="3">
-        <v>1199200</v>
+        <v>1181400</v>
       </c>
       <c r="F18" s="3">
         <v>785700</v>
@@ -1163,7 +1163,7 @@
         <v>927800</v>
       </c>
       <c r="E21" s="3">
-        <v>1323300</v>
+        <v>1305500</v>
       </c>
       <c r="F21" s="3">
         <v>866400</v>
@@ -2442,10 +2442,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>19206900</v>
+        <v>15254100</v>
       </c>
       <c r="E58" s="3">
-        <v>12682400</v>
+        <v>9936700</v>
       </c>
       <c r="F58" s="3">
         <v>9191900</v>
@@ -2481,10 +2481,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>196700</v>
+        <v>4149500</v>
       </c>
       <c r="E59" s="3">
-        <v>153100</v>
+        <v>2898900</v>
       </c>
       <c r="F59" s="3">
         <v>3746200</v>
